--- a/templates/project-content-i18n-template.xlsx
+++ b/templates/project-content-i18n-template.xlsx
@@ -1,17 +1,49 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <sheets>
-    <sheet sheetId="1" name="Project translations" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
-  </sheets>
-  <calcPr calcId="171027"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>2</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="2" baseType="lpstr">
+      <vt:lpstr>Project translations</vt:lpstr>
+      <vt:lpstr>Instructions</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <Manager/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Setin Studio</dc:creator>
+  <dc:title/>
+  <dc:subject/>
+  <dc:description/>
+  <cp:keywords/>
+  <cp:category/>
+  <cp:lastModifiedBy>Unknown</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-10T00:03:36Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-10T00:03:36Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="44">
   <si>
     <t>Block</t>
@@ -140,15 +172,21 @@
     <t>5. Hero Title = project hero headline.</t>
   </si>
   <si>
-    <t>6. Meta: Services, Industry, Market, Year.</t>
+    <t>6. Meta: Services, Industry, Market, Year, Live (adres strony, ten sam we wszystkich językach).</t>
   </si>
   <si>
     <t>7. One sheet = one project. Duplicate "Project translations" for more projects.</t>
+  </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t>Adres live, np. nrvsystems.com (bez http). Puste = ukryj wiersz na stronie.</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -284,7 +322,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -604,9 +642,21 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="Project translations" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+  </sheets>
+  <calcPr calcId="171027"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -775,24 +825,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>22</v>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -800,7 +850,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>8</v>
@@ -812,47 +862,47 @@
         <v>8</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="C12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -860,7 +910,7 @@
         <v>26</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>8</v>
@@ -875,44 +925,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="11" t="s">
+      <c r="C15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,7 +970,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>8</v>
@@ -935,44 +985,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="C18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -980,7 +1030,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>8</v>
@@ -995,44 +1045,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="C21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,7 +1090,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>8</v>
@@ -1055,44 +1105,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="C24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,7 +1150,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>8</v>
@@ -1115,44 +1165,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="11" t="s">
+      <c r="C27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1160,7 +1210,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
@@ -1175,44 +1225,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="9" t="s">
+      <c r="C30" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1220,7 +1270,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>8</v>
@@ -1235,44 +1285,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="C33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,7 +1330,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>8</v>
@@ -1295,44 +1345,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="9" t="s">
+      <c r="C36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1340,7 +1390,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>8</v>
@@ -1352,26 +1402,46 @@
         <v>8</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="C39" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="11" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1381,7 +1451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
